--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38843-2026 artfynd.xlsx
+++ b/artfynd/A 38843-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170982</v>
       </c>
       <c r="B2" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137170905</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
